--- a/scripts/files/create_payments_new_2024_test.xlsx
+++ b/scripts/files/create_payments_new_2024_test.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="49">
   <si>
     <t>Transaction date</t>
   </si>
@@ -37,49 +37,19 @@
     <t>Amount</t>
   </si>
   <si>
-    <t>30/01/2024</t>
+    <t>27/02/2024</t>
   </si>
   <si>
     <t>Payment</t>
   </si>
   <si>
-    <t>EAUR/8090/S22</t>
+    <t>24100569 (deleted)</t>
   </si>
   <si>
     <t>Undeposited Funds</t>
   </si>
   <si>
     <t>32.1011 Accounts Receivable_KGL</t>
-  </si>
-  <si>
-    <t>26/02/2024</t>
-  </si>
-  <si>
-    <t>24100351 (deleted)</t>
-  </si>
-  <si>
-    <t>24900063 (deleted)</t>
-  </si>
-  <si>
-    <t>24900328 (deleted)</t>
-  </si>
-  <si>
-    <t>24900150 (deleted)</t>
-  </si>
-  <si>
-    <t>23100456 (deleted-2)</t>
-  </si>
-  <si>
-    <t>23500919 (deleted)</t>
-  </si>
-  <si>
-    <t>27/02/2024</t>
-  </si>
-  <si>
-    <t>23100067 (deleted-2)</t>
-  </si>
-  <si>
-    <t>24100569 (deleted)</t>
   </si>
   <si>
     <t>24100571 (deleted)</t>
@@ -236,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -251,9 +221,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -524,8 +491,8 @@
         <v>9</v>
       </c>
       <c r="C2" s="3">
-        <f t="shared" ref="C2:C58" si="1">RANDBETWEEN(10000,999999)</f>
-        <v>940203</v>
+        <f t="shared" ref="C2:C50" si="1">RANDBETWEEN(10000,999999)</f>
+        <v>748514</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>10</v>
@@ -538,7 +505,7 @@
         <v>12</v>
       </c>
       <c r="H2" s="4">
-        <v>40000.0</v>
+        <v>70000.0</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -561,17 +528,17 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="3">
         <f t="shared" si="1"/>
-        <v>29691</v>
+        <v>333611</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="3" t="s">
@@ -604,17 +571,17 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="3">
         <f t="shared" si="1"/>
-        <v>439215</v>
+        <v>68529</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="3" t="s">
@@ -624,7 +591,7 @@
         <v>12</v>
       </c>
       <c r="H4" s="4">
-        <v>10000.0</v>
+        <v>54000.0</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
@@ -647,17 +614,17 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="3">
         <f t="shared" si="1"/>
-        <v>310930</v>
+        <v>556896</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="3" t="s">
@@ -667,7 +634,7 @@
         <v>12</v>
       </c>
       <c r="H5" s="4">
-        <v>90000.0</v>
+        <v>45000.0</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -690,17 +657,17 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="3">
         <f t="shared" si="1"/>
-        <v>173821</v>
+        <v>63196</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>17</v>
+      <c r="D6" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="3" t="s">
@@ -710,7 +677,7 @@
         <v>12</v>
       </c>
       <c r="H6" s="4">
-        <v>60000.0</v>
+        <v>45000.0</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
@@ -733,17 +700,17 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="3">
         <f t="shared" si="1"/>
-        <v>675393</v>
+        <v>99334</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="3" t="s">
@@ -753,7 +720,7 @@
         <v>12</v>
       </c>
       <c r="H7" s="4">
-        <v>65000.0</v>
+        <v>54000.0</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
@@ -776,17 +743,17 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="3">
         <f t="shared" si="1"/>
-        <v>134603</v>
+        <v>195552</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="3" t="s">
@@ -796,7 +763,7 @@
         <v>12</v>
       </c>
       <c r="H8" s="4">
-        <v>10000.0</v>
+        <v>45000.0</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
@@ -819,17 +786,17 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" si="1"/>
-        <v>288525</v>
+        <v>280577</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="3" t="s">
@@ -839,7 +806,7 @@
         <v>12</v>
       </c>
       <c r="H9" s="4">
-        <v>700000.0</v>
+        <v>45000.0</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
@@ -862,17 +829,17 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="1"/>
-        <v>293054</v>
+        <v>435332</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="3" t="s">
@@ -882,7 +849,7 @@
         <v>12</v>
       </c>
       <c r="H10" s="4">
-        <v>70000.0</v>
+        <v>45000.0</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
@@ -905,17 +872,17 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="1"/>
-        <v>977659</v>
+        <v>380258</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="3" t="s">
@@ -925,7 +892,7 @@
         <v>12</v>
       </c>
       <c r="H11" s="4">
-        <v>45000.0</v>
+        <v>180000.0</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
@@ -948,17 +915,17 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="1"/>
-        <v>974916</v>
+        <v>43741</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="3" t="s">
@@ -968,7 +935,7 @@
         <v>12</v>
       </c>
       <c r="H12" s="4">
-        <v>54000.0</v>
+        <v>45000.0</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
@@ -991,17 +958,17 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="3">
         <f t="shared" si="1"/>
-        <v>240226</v>
+        <v>950456</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="3" t="s">
@@ -1011,7 +978,7 @@
         <v>12</v>
       </c>
       <c r="H13" s="4">
-        <v>45000.0</v>
+        <v>218000.0</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
@@ -1034,17 +1001,17 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="3">
         <f t="shared" si="1"/>
-        <v>978552</v>
+        <v>674199</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="3" t="s">
@@ -1077,17 +1044,17 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" si="1"/>
-        <v>213909</v>
+        <v>14259</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="3" t="s">
@@ -1097,7 +1064,7 @@
         <v>12</v>
       </c>
       <c r="H15" s="4">
-        <v>54000.0</v>
+        <v>263000.0</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
@@ -1120,17 +1087,17 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="3">
         <f t="shared" si="1"/>
-        <v>958813</v>
+        <v>839319</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="3" t="s">
@@ -1140,7 +1107,7 @@
         <v>12</v>
       </c>
       <c r="H16" s="4">
-        <v>45000.0</v>
+        <v>180000.0</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -1163,17 +1130,17 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="3">
         <f t="shared" si="1"/>
-        <v>975360</v>
+        <v>874437</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="3" t="s">
@@ -1206,17 +1173,17 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="3">
         <f t="shared" si="1"/>
-        <v>258777</v>
+        <v>616247</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="3" t="s">
@@ -1249,17 +1216,17 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="3">
         <f t="shared" si="1"/>
-        <v>283099</v>
+        <v>528675</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="3" t="s">
@@ -1269,7 +1236,7 @@
         <v>12</v>
       </c>
       <c r="H19" s="4">
-        <v>180000.0</v>
+        <v>54000.0</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -1292,17 +1259,17 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" si="1"/>
-        <v>957274</v>
+        <v>175096</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="3" t="s">
@@ -1335,17 +1302,17 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="1"/>
-        <v>432698</v>
+        <v>241228</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="3" t="s">
@@ -1355,7 +1322,7 @@
         <v>12</v>
       </c>
       <c r="H21" s="4">
-        <v>218000.0</v>
+        <v>45000.0</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
@@ -1378,17 +1345,17 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" si="1"/>
-        <v>349885</v>
+        <v>426390</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="3" t="s">
@@ -1421,17 +1388,17 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="1"/>
-        <v>437576</v>
+        <v>47281</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="3" t="s">
@@ -1441,7 +1408,7 @@
         <v>12</v>
       </c>
       <c r="H23" s="4">
-        <v>263000.0</v>
+        <v>50000.0</v>
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
@@ -1464,17 +1431,17 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="3">
         <f t="shared" si="1"/>
-        <v>44607</v>
+        <v>196206</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="3" t="s">
@@ -1484,7 +1451,7 @@
         <v>12</v>
       </c>
       <c r="H24" s="4">
-        <v>180000.0</v>
+        <v>26000.0</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
@@ -1507,17 +1474,17 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="3">
         <f t="shared" si="1"/>
-        <v>263571</v>
+        <v>161929</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="3" t="s">
@@ -1527,7 +1494,7 @@
         <v>12</v>
       </c>
       <c r="H25" s="4">
-        <v>45000.0</v>
+        <v>30000.0</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
@@ -1550,17 +1517,17 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="3">
         <f t="shared" si="1"/>
-        <v>637034</v>
+        <v>828348</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" s="3" t="s">
@@ -1570,7 +1537,7 @@
         <v>12</v>
       </c>
       <c r="H26" s="4">
-        <v>45000.0</v>
+        <v>20000.0</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
@@ -1593,17 +1560,17 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C27" s="3">
         <f t="shared" si="1"/>
-        <v>692661</v>
+        <v>938395</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="3" t="s">
@@ -1613,7 +1580,7 @@
         <v>12</v>
       </c>
       <c r="H27" s="4">
-        <v>54000.0</v>
+        <v>45000.0</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
@@ -1636,17 +1603,17 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C28" s="3">
         <f t="shared" si="1"/>
-        <v>434313</v>
+        <v>927823</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" s="3" t="s">
@@ -1679,17 +1646,17 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C29" s="3">
         <f t="shared" si="1"/>
-        <v>16063</v>
+        <v>137134</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="3" t="s">
@@ -1699,7 +1666,7 @@
         <v>12</v>
       </c>
       <c r="H29" s="4">
-        <v>45000.0</v>
+        <v>150000.0</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
@@ -1722,17 +1689,17 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C30" s="3">
         <f t="shared" si="1"/>
-        <v>644500</v>
+        <v>943816</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="3" t="s">
@@ -1742,7 +1709,7 @@
         <v>12</v>
       </c>
       <c r="H30" s="4">
-        <v>45000.0</v>
+        <v>55000.0</v>
       </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
@@ -1765,17 +1732,17 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="3">
         <f t="shared" si="1"/>
-        <v>335540</v>
+        <v>822537</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="3" t="s">
@@ -1785,7 +1752,7 @@
         <v>12</v>
       </c>
       <c r="H31" s="4">
-        <v>50000.0</v>
+        <v>388000.0</v>
       </c>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
@@ -1808,17 +1775,17 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="3">
         <f t="shared" si="1"/>
-        <v>309912</v>
+        <v>813239</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="3" t="s">
@@ -1828,7 +1795,7 @@
         <v>12</v>
       </c>
       <c r="H32" s="4">
-        <v>26000.0</v>
+        <v>10.0</v>
       </c>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
@@ -1851,17 +1818,17 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="3">
         <f t="shared" si="1"/>
-        <v>468032</v>
+        <v>175248</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="3" t="s">
@@ -1871,7 +1838,7 @@
         <v>12</v>
       </c>
       <c r="H33" s="4">
-        <v>30000.0</v>
+        <v>70000.0</v>
       </c>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
@@ -1894,17 +1861,17 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="3">
         <f t="shared" si="1"/>
-        <v>937699</v>
+        <v>800782</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="3" t="s">
@@ -1914,7 +1881,7 @@
         <v>12</v>
       </c>
       <c r="H34" s="4">
-        <v>20000.0</v>
+        <v>30500.0</v>
       </c>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
@@ -1937,17 +1904,17 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="3">
         <f t="shared" si="1"/>
-        <v>261997</v>
+        <v>375392</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="3" t="s">
@@ -1957,7 +1924,7 @@
         <v>12</v>
       </c>
       <c r="H35" s="4">
-        <v>45000.0</v>
+        <v>20000.0</v>
       </c>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
@@ -1980,17 +1947,17 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="3">
         <f t="shared" si="1"/>
-        <v>740829</v>
+        <v>791634</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="3" t="s">
@@ -2000,7 +1967,7 @@
         <v>12</v>
       </c>
       <c r="H36" s="4">
-        <v>45000.0</v>
+        <v>20000.0</v>
       </c>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
@@ -2023,17 +1990,17 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="3">
         <f t="shared" si="1"/>
-        <v>826593</v>
+        <v>524262</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="3" t="s">
@@ -2043,7 +2010,7 @@
         <v>12</v>
       </c>
       <c r="H37" s="4">
-        <v>150000.0</v>
+        <v>45000.0</v>
       </c>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
@@ -2066,17 +2033,17 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="3">
         <f t="shared" si="1"/>
-        <v>71896</v>
+        <v>490239</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="3" t="s">
@@ -2086,7 +2053,7 @@
         <v>12</v>
       </c>
       <c r="H38" s="4">
-        <v>55000.0</v>
+        <v>100000.0</v>
       </c>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
@@ -2109,17 +2076,17 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="3">
         <f t="shared" si="1"/>
-        <v>359846</v>
+        <v>965024</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="3" t="s">
@@ -2129,7 +2096,7 @@
         <v>12</v>
       </c>
       <c r="H39" s="4">
-        <v>388000.0</v>
+        <v>50000.0</v>
       </c>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
@@ -2152,17 +2119,17 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="3">
         <f t="shared" si="1"/>
-        <v>814271</v>
+        <v>109306</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="3" t="s">
@@ -2172,7 +2139,7 @@
         <v>12</v>
       </c>
       <c r="H40" s="4">
-        <v>10.0</v>
+        <v>100000.0</v>
       </c>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
@@ -2195,17 +2162,17 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="3">
         <f t="shared" si="1"/>
-        <v>329997</v>
+        <v>526669</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="3" t="s">
@@ -2215,7 +2182,7 @@
         <v>12</v>
       </c>
       <c r="H41" s="4">
-        <v>70000.0</v>
+        <v>66100.0</v>
       </c>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
@@ -2238,17 +2205,17 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="3">
         <f t="shared" si="1"/>
-        <v>359983</v>
+        <v>867896</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="3" t="s">
@@ -2258,7 +2225,7 @@
         <v>12</v>
       </c>
       <c r="H42" s="4">
-        <v>30500.0</v>
+        <v>5000.0</v>
       </c>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
@@ -2281,17 +2248,17 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="3">
         <f t="shared" si="1"/>
-        <v>81680</v>
+        <v>331489</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="3" t="s">
@@ -2301,7 +2268,7 @@
         <v>12</v>
       </c>
       <c r="H43" s="4">
-        <v>20000.0</v>
+        <v>1448500.0</v>
       </c>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
@@ -2324,17 +2291,17 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="3">
         <f t="shared" si="1"/>
-        <v>105919</v>
+        <v>335931</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="3" t="s">
@@ -2344,7 +2311,7 @@
         <v>12</v>
       </c>
       <c r="H44" s="4">
-        <v>20000.0</v>
+        <v>200000.0</v>
       </c>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
@@ -2367,17 +2334,17 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="3">
         <f t="shared" si="1"/>
-        <v>294607</v>
+        <v>745588</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="3" t="s">
@@ -2387,7 +2354,7 @@
         <v>12</v>
       </c>
       <c r="H45" s="4">
-        <v>45000.0</v>
+        <v>20000.0</v>
       </c>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
@@ -2410,17 +2377,17 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="3">
         <f t="shared" si="1"/>
-        <v>915253</v>
+        <v>133311</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="3" t="s">
@@ -2430,7 +2397,7 @@
         <v>12</v>
       </c>
       <c r="H46" s="4">
-        <v>100000.0</v>
+        <v>20000.0</v>
       </c>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
@@ -2453,17 +2420,17 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="3">
         <f t="shared" si="1"/>
-        <v>326807</v>
+        <v>512093</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" s="3" t="s">
@@ -2473,7 +2440,7 @@
         <v>12</v>
       </c>
       <c r="H47" s="4">
-        <v>50000.0</v>
+        <v>20000.0</v>
       </c>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
@@ -2496,17 +2463,17 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C48" s="3">
         <f t="shared" si="1"/>
-        <v>364954</v>
+        <v>738742</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" s="3" t="s">
@@ -2516,7 +2483,7 @@
         <v>12</v>
       </c>
       <c r="H48" s="4">
-        <v>100000.0</v>
+        <v>20000.0</v>
       </c>
       <c r="I48" s="2"/>
       <c r="J48" s="2"/>
@@ -2539,17 +2506,17 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C49" s="3">
         <f t="shared" si="1"/>
-        <v>314832</v>
+        <v>329496</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="3" t="s">
@@ -2559,7 +2526,7 @@
         <v>12</v>
       </c>
       <c r="H49" s="4">
-        <v>66100.0</v>
+        <v>532500.0</v>
       </c>
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
@@ -2582,17 +2549,17 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C50" s="3">
         <f t="shared" si="1"/>
-        <v>844584</v>
+        <v>33136</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="3" t="s">
@@ -2602,7 +2569,7 @@
         <v>12</v>
       </c>
       <c r="H50" s="4">
-        <v>5000.0</v>
+        <v>300000.0</v>
       </c>
       <c r="I50" s="2"/>
       <c r="J50" s="2"/>
@@ -2624,29 +2591,14 @@
       <c r="Z50" s="2"/>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C51" s="3">
-        <f t="shared" si="1"/>
-        <v>452870</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H51" s="4">
-        <v>1448500.0</v>
-      </c>
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="4"/>
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
@@ -2667,29 +2619,14 @@
       <c r="Z51" s="2"/>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C52" s="3">
-        <f t="shared" si="1"/>
-        <v>772699</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H52" s="4">
-        <v>200000.0</v>
-      </c>
+      <c r="A52" s="3"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="4"/>
       <c r="I52" s="2"/>
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
@@ -2710,29 +2647,14 @@
       <c r="Z52" s="2"/>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C53" s="3">
-        <f t="shared" si="1"/>
-        <v>67530</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H53" s="4">
-        <v>20000.0</v>
-      </c>
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="4"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
@@ -2753,29 +2675,14 @@
       <c r="Z53" s="2"/>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C54" s="3">
-        <f t="shared" si="1"/>
-        <v>222866</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H54" s="4">
-        <v>20000.0</v>
-      </c>
+      <c r="A54" s="3"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="4"/>
       <c r="I54" s="2"/>
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
@@ -2796,29 +2703,14 @@
       <c r="Z54" s="2"/>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C55" s="3">
-        <f t="shared" si="1"/>
-        <v>511752</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H55" s="4">
-        <v>20000.0</v>
-      </c>
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="4"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
@@ -2839,29 +2731,14 @@
       <c r="Z55" s="2"/>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C56" s="3">
-        <f t="shared" si="1"/>
-        <v>478753</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H56" s="4">
-        <v>20000.0</v>
-      </c>
+      <c r="A56" s="3"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="4"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
@@ -2882,29 +2759,14 @@
       <c r="Z56" s="2"/>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C57" s="3">
-        <f t="shared" si="1"/>
-        <v>554425</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H57" s="4">
-        <v>532500.0</v>
-      </c>
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="4"/>
       <c r="I57" s="2"/>
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
@@ -2925,29 +2787,14 @@
       <c r="Z57" s="2"/>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C58" s="3">
-        <f t="shared" si="1"/>
-        <v>270850</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H58" s="4">
-        <v>300000.0</v>
-      </c>
+      <c r="A58" s="3"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="4"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
@@ -68712,14 +68559,14 @@
       <c r="Z2406" s="2"/>
     </row>
     <row r="2407">
-      <c r="A2407" s="3"/>
-      <c r="B2407" s="3"/>
-      <c r="C2407" s="3"/>
-      <c r="D2407" s="3"/>
-      <c r="E2407" s="3"/>
-      <c r="F2407" s="3"/>
-      <c r="G2407" s="3"/>
-      <c r="H2407" s="4"/>
+      <c r="A2407" s="2"/>
+      <c r="B2407" s="2"/>
+      <c r="C2407" s="2"/>
+      <c r="D2407" s="2"/>
+      <c r="E2407" s="2"/>
+      <c r="F2407" s="2"/>
+      <c r="G2407" s="2"/>
+      <c r="H2407" s="2"/>
       <c r="I2407" s="2"/>
       <c r="J2407" s="2"/>
       <c r="K2407" s="2"/>
@@ -68740,14 +68587,14 @@
       <c r="Z2407" s="2"/>
     </row>
     <row r="2408">
-      <c r="A2408" s="3"/>
-      <c r="B2408" s="3"/>
-      <c r="C2408" s="3"/>
-      <c r="D2408" s="3"/>
-      <c r="E2408" s="3"/>
-      <c r="F2408" s="3"/>
-      <c r="G2408" s="3"/>
-      <c r="H2408" s="4"/>
+      <c r="A2408" s="2"/>
+      <c r="B2408" s="2"/>
+      <c r="C2408" s="2"/>
+      <c r="D2408" s="2"/>
+      <c r="E2408" s="2"/>
+      <c r="F2408" s="2"/>
+      <c r="G2408" s="2"/>
+      <c r="H2408" s="2"/>
       <c r="I2408" s="2"/>
       <c r="J2408" s="2"/>
       <c r="K2408" s="2"/>
@@ -68767,230 +68614,6 @@
       <c r="Y2408" s="2"/>
       <c r="Z2408" s="2"/>
     </row>
-    <row r="2409">
-      <c r="A2409" s="3"/>
-      <c r="B2409" s="3"/>
-      <c r="C2409" s="3"/>
-      <c r="D2409" s="3"/>
-      <c r="E2409" s="3"/>
-      <c r="F2409" s="3"/>
-      <c r="G2409" s="3"/>
-      <c r="H2409" s="4"/>
-      <c r="I2409" s="2"/>
-      <c r="J2409" s="2"/>
-      <c r="K2409" s="2"/>
-      <c r="L2409" s="2"/>
-      <c r="M2409" s="2"/>
-      <c r="N2409" s="2"/>
-      <c r="O2409" s="2"/>
-      <c r="P2409" s="2"/>
-      <c r="Q2409" s="2"/>
-      <c r="R2409" s="2"/>
-      <c r="S2409" s="2"/>
-      <c r="T2409" s="2"/>
-      <c r="U2409" s="2"/>
-      <c r="V2409" s="2"/>
-      <c r="W2409" s="2"/>
-      <c r="X2409" s="2"/>
-      <c r="Y2409" s="2"/>
-      <c r="Z2409" s="2"/>
-    </row>
-    <row r="2410">
-      <c r="A2410" s="3"/>
-      <c r="B2410" s="3"/>
-      <c r="C2410" s="3"/>
-      <c r="D2410" s="3"/>
-      <c r="E2410" s="3"/>
-      <c r="F2410" s="3"/>
-      <c r="G2410" s="3"/>
-      <c r="H2410" s="4"/>
-      <c r="I2410" s="2"/>
-      <c r="J2410" s="2"/>
-      <c r="K2410" s="2"/>
-      <c r="L2410" s="2"/>
-      <c r="M2410" s="2"/>
-      <c r="N2410" s="2"/>
-      <c r="O2410" s="2"/>
-      <c r="P2410" s="2"/>
-      <c r="Q2410" s="2"/>
-      <c r="R2410" s="2"/>
-      <c r="S2410" s="2"/>
-      <c r="T2410" s="2"/>
-      <c r="U2410" s="2"/>
-      <c r="V2410" s="2"/>
-      <c r="W2410" s="2"/>
-      <c r="X2410" s="2"/>
-      <c r="Y2410" s="2"/>
-      <c r="Z2410" s="2"/>
-    </row>
-    <row r="2411">
-      <c r="A2411" s="3"/>
-      <c r="B2411" s="3"/>
-      <c r="C2411" s="3"/>
-      <c r="D2411" s="3"/>
-      <c r="E2411" s="3"/>
-      <c r="F2411" s="3"/>
-      <c r="G2411" s="3"/>
-      <c r="H2411" s="4"/>
-      <c r="I2411" s="2"/>
-      <c r="J2411" s="2"/>
-      <c r="K2411" s="2"/>
-      <c r="L2411" s="2"/>
-      <c r="M2411" s="2"/>
-      <c r="N2411" s="2"/>
-      <c r="O2411" s="2"/>
-      <c r="P2411" s="2"/>
-      <c r="Q2411" s="2"/>
-      <c r="R2411" s="2"/>
-      <c r="S2411" s="2"/>
-      <c r="T2411" s="2"/>
-      <c r="U2411" s="2"/>
-      <c r="V2411" s="2"/>
-      <c r="W2411" s="2"/>
-      <c r="X2411" s="2"/>
-      <c r="Y2411" s="2"/>
-      <c r="Z2411" s="2"/>
-    </row>
-    <row r="2412">
-      <c r="A2412" s="3"/>
-      <c r="B2412" s="3"/>
-      <c r="C2412" s="3"/>
-      <c r="D2412" s="3"/>
-      <c r="E2412" s="3"/>
-      <c r="F2412" s="3"/>
-      <c r="G2412" s="3"/>
-      <c r="H2412" s="4"/>
-      <c r="I2412" s="2"/>
-      <c r="J2412" s="2"/>
-      <c r="K2412" s="2"/>
-      <c r="L2412" s="2"/>
-      <c r="M2412" s="2"/>
-      <c r="N2412" s="2"/>
-      <c r="O2412" s="2"/>
-      <c r="P2412" s="2"/>
-      <c r="Q2412" s="2"/>
-      <c r="R2412" s="2"/>
-      <c r="S2412" s="2"/>
-      <c r="T2412" s="2"/>
-      <c r="U2412" s="2"/>
-      <c r="V2412" s="2"/>
-      <c r="W2412" s="2"/>
-      <c r="X2412" s="2"/>
-      <c r="Y2412" s="2"/>
-      <c r="Z2412" s="2"/>
-    </row>
-    <row r="2413">
-      <c r="A2413" s="3"/>
-      <c r="B2413" s="3"/>
-      <c r="C2413" s="3"/>
-      <c r="D2413" s="3"/>
-      <c r="E2413" s="3"/>
-      <c r="F2413" s="3"/>
-      <c r="G2413" s="3"/>
-      <c r="H2413" s="4"/>
-      <c r="I2413" s="2"/>
-      <c r="J2413" s="2"/>
-      <c r="K2413" s="2"/>
-      <c r="L2413" s="2"/>
-      <c r="M2413" s="2"/>
-      <c r="N2413" s="2"/>
-      <c r="O2413" s="2"/>
-      <c r="P2413" s="2"/>
-      <c r="Q2413" s="2"/>
-      <c r="R2413" s="2"/>
-      <c r="S2413" s="2"/>
-      <c r="T2413" s="2"/>
-      <c r="U2413" s="2"/>
-      <c r="V2413" s="2"/>
-      <c r="W2413" s="2"/>
-      <c r="X2413" s="2"/>
-      <c r="Y2413" s="2"/>
-      <c r="Z2413" s="2"/>
-    </row>
-    <row r="2414">
-      <c r="A2414" s="3"/>
-      <c r="B2414" s="3"/>
-      <c r="C2414" s="3"/>
-      <c r="D2414" s="3"/>
-      <c r="E2414" s="3"/>
-      <c r="F2414" s="3"/>
-      <c r="G2414" s="3"/>
-      <c r="H2414" s="4"/>
-      <c r="I2414" s="2"/>
-      <c r="J2414" s="2"/>
-      <c r="K2414" s="2"/>
-      <c r="L2414" s="2"/>
-      <c r="M2414" s="2"/>
-      <c r="N2414" s="2"/>
-      <c r="O2414" s="2"/>
-      <c r="P2414" s="2"/>
-      <c r="Q2414" s="2"/>
-      <c r="R2414" s="2"/>
-      <c r="S2414" s="2"/>
-      <c r="T2414" s="2"/>
-      <c r="U2414" s="2"/>
-      <c r="V2414" s="2"/>
-      <c r="W2414" s="2"/>
-      <c r="X2414" s="2"/>
-      <c r="Y2414" s="2"/>
-      <c r="Z2414" s="2"/>
-    </row>
-    <row r="2415">
-      <c r="A2415" s="2"/>
-      <c r="B2415" s="2"/>
-      <c r="C2415" s="2"/>
-      <c r="D2415" s="2"/>
-      <c r="E2415" s="2"/>
-      <c r="F2415" s="2"/>
-      <c r="G2415" s="2"/>
-      <c r="H2415" s="2"/>
-      <c r="I2415" s="2"/>
-      <c r="J2415" s="2"/>
-      <c r="K2415" s="2"/>
-      <c r="L2415" s="2"/>
-      <c r="M2415" s="2"/>
-      <c r="N2415" s="2"/>
-      <c r="O2415" s="2"/>
-      <c r="P2415" s="2"/>
-      <c r="Q2415" s="2"/>
-      <c r="R2415" s="2"/>
-      <c r="S2415" s="2"/>
-      <c r="T2415" s="2"/>
-      <c r="U2415" s="2"/>
-      <c r="V2415" s="2"/>
-      <c r="W2415" s="2"/>
-      <c r="X2415" s="2"/>
-      <c r="Y2415" s="2"/>
-      <c r="Z2415" s="2"/>
-    </row>
-    <row r="2416">
-      <c r="A2416" s="2"/>
-      <c r="B2416" s="2"/>
-      <c r="C2416" s="2"/>
-      <c r="D2416" s="2"/>
-      <c r="E2416" s="2"/>
-      <c r="F2416" s="2"/>
-      <c r="G2416" s="2"/>
-      <c r="H2416" s="2"/>
-      <c r="I2416" s="2"/>
-      <c r="J2416" s="2"/>
-      <c r="K2416" s="2"/>
-      <c r="L2416" s="2"/>
-      <c r="M2416" s="2"/>
-      <c r="N2416" s="2"/>
-      <c r="O2416" s="2"/>
-      <c r="P2416" s="2"/>
-      <c r="Q2416" s="2"/>
-      <c r="R2416" s="2"/>
-      <c r="S2416" s="2"/>
-      <c r="T2416" s="2"/>
-      <c r="U2416" s="2"/>
-      <c r="V2416" s="2"/>
-      <c r="W2416" s="2"/>
-      <c r="X2416" s="2"/>
-      <c r="Y2416" s="2"/>
-      <c r="Z2416" s="2"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
